--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -13937,6 +13937,408 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13970,7 +14372,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14455,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -14063,7 +14465,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -14083,7 +14485,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -14115,7 +14517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -916,9 +916,6 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1168,7 +1165,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1570,7 +1567,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1972,7 +1969,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2374,7 +2371,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2776,7 +2773,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3326,7 +3323,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3728,7 +3725,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4130,7 +4127,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4532,7 +4529,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5082,7 +5079,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5484,7 +5481,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5886,7 +5883,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6288,7 +6285,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6435,9 +6432,6 @@
       <c r="O31" t="n">
         <v>5</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -6838,7 +6832,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7240,7 +7234,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7642,7 +7636,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8044,7 +8038,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8191,9 +8185,6 @@
       <c r="O40" t="n">
         <v>13</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.006087206258028249</v>
       </c>
@@ -8339,9 +8330,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -8742,7 +8730,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9144,7 +9132,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9546,7 +9534,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9948,7 +9936,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10350,7 +10338,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10497,9 +10485,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -10648,9 +10633,6 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10900,7 +10882,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11050,9 +11032,6 @@
       <c r="P55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -11302,7 +11281,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -11452,9 +11431,6 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11704,7 +11680,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11854,9 +11830,6 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -12106,7 +12079,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12253,9 +12226,6 @@
       <c r="O61" t="n">
         <v>4</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -12404,9 +12374,6 @@
       <c r="P62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -12656,7 +12623,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12806,9 +12773,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13058,7 +13022,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13208,9 +13172,6 @@
       <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -13460,7 +13421,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13610,9 +13571,6 @@
       <c r="P68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -13862,7 +13820,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14012,9 +13970,6 @@
       <c r="P70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -14264,7 +14219,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -13923,12 +13923,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -13967,93 +13967,76 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
       <c r="R70" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14063,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14132,98 +14115,23 @@
       <c r="P71" t="n">
         <v>1</v>
       </c>
+      <c r="R71" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN71" t="b">
-        <v>1</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -14289,6 +14197,243 @@
         </is>
       </c>
       <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14410,7 +14555,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -14420,7 +14565,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -14472,7 +14617,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -14439,6 +14439,405 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14472,7 +14871,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14954,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -14565,7 +14964,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -14585,7 +14984,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -10441,12 +10441,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10480,13 +10480,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="R52" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.01498389232745415</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10519,42 +10519,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -10586,12 +10586,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -10625,98 +10625,81 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10726,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10795,98 +10778,23 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN54" t="b">
-        <v>1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -10980,7 +10888,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11015,7 +10923,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -11024,31 +10932,106 @@
         </is>
       </c>
       <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
         <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -11142,7 +11125,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11194,98 +11177,23 @@
       <c r="P56" t="n">
         <v>1</v>
       </c>
+      <c r="R56" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN56" t="b">
-        <v>1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -11379,7 +11287,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11414,7 +11322,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -11423,31 +11331,106 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -11541,7 +11524,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11593,98 +11576,23 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN58" t="b">
-        <v>1</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -11778,7 +11686,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11813,7 +11721,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -11830,23 +11738,98 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -11940,7 +11923,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11992,98 +11975,23 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
-        <v>1</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -12177,17 +12085,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12212,90 +12120,182 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
+        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12357,7 +12357,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -12366,98 +12366,81 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.01779337213885181</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -12484,17 +12467,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12519,7 +12502,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -12528,173 +12511,81 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN63" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12647,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -12765,16 +12656,16 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12918,7 +12809,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -12927,13 +12818,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13155,7 +13046,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -13164,16 +13055,16 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13317,7 +13208,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -13326,13 +13217,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13554,7 +13445,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -13563,16 +13454,16 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13716,7 +13607,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -13725,13 +13616,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -13923,12 +13814,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13953,90 +13844,107 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
         <v>1</v>
       </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP70" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
-      <c r="AT70" t="n">
-        <v>0</v>
-      </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14063,7 +13971,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14098,40 +14006,115 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" t="n">
+        <v>2</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
         <v>1</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -14225,17 +14208,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14260,7 +14243,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -14274,168 +14257,76 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN72" t="b">
-        <v>1</v>
+      <c r="R72" t="n">
+        <v>0.0004682466352329422</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -14467,12 +14358,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14497,7 +14388,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -14506,98 +14397,81 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14498,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14659,7 +14533,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -14668,106 +14542,31 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>1</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -14833,6 +14632,1041 @@
         </is>
       </c>
       <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14871,7 +15705,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14954,7 +15788,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -14964,7 +15798,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -14984,7 +15818,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -15016,7 +15850,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -15672,6 +15672,405 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15705,7 +16104,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -15788,7 +16187,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -15798,7 +16197,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -15818,7 +16217,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
